--- a/results/02_taxa_assemblage/WardsClustering/tables/pvclust_summary.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/pvclust_summary.xlsx
@@ -450,10 +450,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0916638957827715</v>
+        <v>0.0328854555575277</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +461,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.752041676123376</v>
+        <v>0.886603392782555</v>
       </c>
       <c r="C3" t="n">
-        <v>0.271756096857901</v>
+        <v>0.119967580166158</v>
       </c>
     </row>
     <row r="4">
@@ -472,10 +472,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.815054349444824</v>
+        <v>0.718546723494759</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0390502139187556</v>
+        <v>0.0076986691535798</v>
       </c>
     </row>
   </sheetData>
